--- a/전기료_통신비_2026.xlsx
+++ b/전기료_통신비_2026.xlsx
@@ -9,16 +9,17 @@
     <sheet name="인원현황(서울)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="26. 05월" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="26. 05월(통신)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="26. 04월" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="26. 03월" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="26. 02월 " sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="26. 05월(인터넷)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="26. 04월" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="26. 03월" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="26. 02월 " sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'인원현황(서울)'!$A$1:$F$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'26. 05월'!$A$4:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'26. 04월'!$A$4:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26. 03월'!$A$4:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26. 02월 '!$A$4:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'26. 04월'!$A$4:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'26. 03월'!$A$4:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'26. 02월 '!$A$4:$F$12</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
     <numFmt numFmtId="164" formatCode="#,##0_);\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -83,6 +84,10 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -147,16 +152,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -436,6 +441,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -445,7 +478,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -689,23 +722,24 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -714,6 +748,10 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4284,7 +4322,7 @@
   <cols>
     <col width="14.375" customWidth="1" style="53" min="1" max="1"/>
     <col width="10.75" customWidth="1" style="53" min="2" max="2"/>
-    <col width="14" customWidth="1" style="53" min="3" max="3"/>
+    <col width="8.125" customWidth="1" style="53" min="3" max="3"/>
     <col width="12.875" customWidth="1" style="53" min="4" max="4"/>
     <col width="16.75" customWidth="1" style="53" min="5" max="5"/>
     <col width="15.25" customWidth="1" style="53" min="6" max="6"/>
@@ -4305,510 +4343,510 @@
         </is>
       </c>
       <c r="B1" s="83" t="n"/>
-      <c r="C1" s="83" t="n"/>
-      <c r="D1" s="84" t="n">
+      <c r="C1" s="84" t="n"/>
+      <c r="D1" s="85" t="n">
         <v>683340</v>
       </c>
-      <c r="E1" s="84" t="n">
+      <c r="E1" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F1" s="84">
+      <c r="F1" s="85">
         <f>D1+E1</f>
         <v/>
       </c>
-      <c r="I1" s="85" t="inlineStr">
+      <c r="I1" s="86" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="J1" s="85" t="inlineStr">
+      <c r="J1" s="86" t="inlineStr">
         <is>
           <t>층</t>
         </is>
       </c>
-      <c r="K1" s="85" t="inlineStr">
+      <c r="K1" s="86" t="inlineStr">
         <is>
           <t>부서명(본부)</t>
         </is>
       </c>
-      <c r="L1" s="85" t="inlineStr">
+      <c r="L1" s="86" t="inlineStr">
         <is>
           <t>부서명(실이하)</t>
         </is>
       </c>
-      <c r="M1" s="85" t="inlineStr">
+      <c r="M1" s="86" t="inlineStr">
         <is>
           <t>성명</t>
         </is>
       </c>
-      <c r="N1" s="85" t="inlineStr">
+      <c r="N1" s="86" t="inlineStr">
         <is>
           <t>직위</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" s="86" t="n">
+      <c r="I2" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="86" t="inlineStr">
+      <c r="J2" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K2" s="86" t="inlineStr">
+      <c r="K2" s="87" t="inlineStr">
         <is>
           <t>감사역</t>
         </is>
       </c>
-      <c r="L2" s="86" t="inlineStr">
+      <c r="L2" s="87" t="inlineStr">
         <is>
           <t>감사역</t>
         </is>
       </c>
-      <c r="M2" s="86" t="inlineStr">
+      <c r="M2" s="87" t="inlineStr">
         <is>
           <t>김태우</t>
         </is>
       </c>
-      <c r="N2" s="86" t="inlineStr">
+      <c r="N2" s="87" t="inlineStr">
         <is>
           <t>상무</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="87" t="inlineStr">
+      <c r="A3" s="88" t="inlineStr">
         <is>
           <t>성명</t>
         </is>
       </c>
-      <c r="B3" s="87" t="inlineStr">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>계정</t>
         </is>
       </c>
-      <c r="C3" s="87" t="inlineStr">
+      <c r="C3" s="88" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="D3" s="87" t="inlineStr">
+      <c r="D3" s="88" t="inlineStr">
         <is>
           <t>공급가</t>
         </is>
       </c>
-      <c r="E3" s="87" t="inlineStr">
+      <c r="E3" s="88" t="inlineStr">
         <is>
           <t>부가세</t>
         </is>
       </c>
-      <c r="F3" s="87" t="inlineStr">
+      <c r="F3" s="88" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="I3" s="86" t="n">
+      <c r="I3" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="86" t="inlineStr">
+      <c r="J3" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K3" s="86" t="inlineStr">
+      <c r="K3" s="87" t="inlineStr">
         <is>
           <t>R&amp;D본부</t>
         </is>
       </c>
-      <c r="L3" s="86" t="inlineStr">
+      <c r="L3" s="87" t="inlineStr">
         <is>
           <t>R&amp;D본부</t>
         </is>
       </c>
-      <c r="M3" s="86" t="inlineStr">
+      <c r="M3" s="87" t="inlineStr">
         <is>
           <t>김갑득</t>
         </is>
       </c>
-      <c r="N3" s="86" t="inlineStr">
+      <c r="N3" s="87" t="inlineStr">
         <is>
           <t>사장</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="89" t="inlineStr">
         <is>
           <t>이총명</t>
         </is>
       </c>
-      <c r="B4" s="86" t="inlineStr">
+      <c r="B4" s="87" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C4" s="86" t="inlineStr">
+      <c r="C4" s="87" t="inlineStr">
         <is>
           <t>010-4505-2129</t>
         </is>
       </c>
-      <c r="D4" s="89" t="n">
+      <c r="D4" s="90" t="n">
         <v>70960</v>
       </c>
-      <c r="E4" s="89" t="n">
+      <c r="E4" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="89">
+      <c r="F4" s="90">
         <f>D4+E4</f>
         <v/>
       </c>
-      <c r="I4" s="86" t="n">
+      <c r="I4" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="86" t="inlineStr">
+      <c r="J4" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K4" s="86" t="n"/>
-      <c r="L4" s="86" t="inlineStr">
+      <c r="K4" s="87" t="n"/>
+      <c r="L4" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M4" s="86" t="inlineStr">
+      <c r="M4" s="87" t="inlineStr">
         <is>
           <t>김명진</t>
         </is>
       </c>
-      <c r="N4" s="86" t="inlineStr">
+      <c r="N4" s="87" t="inlineStr">
         <is>
           <t>상무</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="89" t="inlineStr">
         <is>
           <t>주현철</t>
         </is>
       </c>
-      <c r="B5" s="86" t="inlineStr">
+      <c r="B5" s="87" t="inlineStr">
         <is>
           <t>판관</t>
         </is>
       </c>
-      <c r="C5" s="86" t="inlineStr">
+      <c r="C5" s="87" t="inlineStr">
         <is>
           <t>010-2858-3989</t>
         </is>
       </c>
-      <c r="D5" s="89" t="n">
+      <c r="D5" s="90" t="n">
         <v>156220</v>
       </c>
-      <c r="E5" s="89" t="n">
+      <c r="E5" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="90">
         <f>D5+E5</f>
         <v/>
       </c>
-      <c r="I5" s="86" t="n">
+      <c r="I5" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="86" t="inlineStr">
+      <c r="J5" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K5" s="86" t="n"/>
-      <c r="L5" s="86" t="inlineStr">
+      <c r="K5" s="87" t="n"/>
+      <c r="L5" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M5" s="86" t="inlineStr">
+      <c r="M5" s="87" t="inlineStr">
         <is>
           <t>이재영</t>
         </is>
       </c>
-      <c r="N5" s="86" t="inlineStr">
+      <c r="N5" s="87" t="inlineStr">
         <is>
           <t>과장</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="88" t="inlineStr">
+      <c r="A6" s="89" t="inlineStr">
         <is>
           <t>강성을</t>
         </is>
       </c>
-      <c r="B6" s="86" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C6" s="86" t="inlineStr">
+      <c r="C6" s="87" t="inlineStr">
         <is>
           <t>010-4791-7943</t>
         </is>
       </c>
-      <c r="D6" s="89" t="n">
+      <c r="D6" s="90" t="n">
         <v>148560</v>
       </c>
-      <c r="E6" s="89" t="n">
+      <c r="E6" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="90">
         <f>D6+E6</f>
         <v/>
       </c>
-      <c r="I6" s="86" t="n">
+      <c r="I6" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="86" t="inlineStr">
+      <c r="J6" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K6" s="86" t="n"/>
-      <c r="L6" s="86" t="inlineStr">
+      <c r="K6" s="87" t="n"/>
+      <c r="L6" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M6" s="86" t="inlineStr">
+      <c r="M6" s="87" t="inlineStr">
         <is>
           <t>강지혜</t>
         </is>
       </c>
-      <c r="N6" s="86" t="inlineStr">
+      <c r="N6" s="87" t="inlineStr">
         <is>
           <t>대리</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>오진택</t>
         </is>
       </c>
-      <c r="B7" s="86" t="inlineStr">
+      <c r="B7" s="87" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C7" s="86" t="inlineStr">
+      <c r="C7" s="87" t="inlineStr">
         <is>
           <t>010-5135-5267</t>
         </is>
       </c>
-      <c r="D7" s="89" t="n">
+      <c r="D7" s="90" t="n">
         <v>88320</v>
       </c>
-      <c r="E7" s="89" t="n">
+      <c r="E7" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="89">
+      <c r="F7" s="90">
         <f>D7+E7</f>
         <v/>
       </c>
-      <c r="I7" s="86" t="n">
+      <c r="I7" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="86" t="inlineStr">
+      <c r="J7" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K7" s="86" t="n"/>
-      <c r="L7" s="86" t="inlineStr">
+      <c r="K7" s="87" t="n"/>
+      <c r="L7" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M7" s="86" t="inlineStr">
+      <c r="M7" s="87" t="inlineStr">
         <is>
           <t>이경태</t>
         </is>
       </c>
-      <c r="N7" s="86" t="inlineStr">
+      <c r="N7" s="87" t="inlineStr">
         <is>
           <t>차장</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="88" t="inlineStr">
+      <c r="A8" s="89" t="inlineStr">
         <is>
           <t>이봉구</t>
         </is>
       </c>
-      <c r="B8" s="86" t="inlineStr">
+      <c r="B8" s="87" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C8" s="86" t="inlineStr">
+      <c r="C8" s="87" t="inlineStr">
         <is>
           <t>010-3731-8303</t>
         </is>
       </c>
-      <c r="D8" s="89" t="n">
+      <c r="D8" s="90" t="n">
         <v>65520</v>
       </c>
-      <c r="E8" s="89" t="n">
+      <c r="E8" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="90">
         <f>D8+E8</f>
         <v/>
       </c>
-      <c r="I8" s="86" t="n">
+      <c r="I8" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="86" t="inlineStr">
+      <c r="J8" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K8" s="86" t="n"/>
-      <c r="L8" s="86" t="inlineStr">
+      <c r="K8" s="87" t="n"/>
+      <c r="L8" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M8" s="86" t="inlineStr">
+      <c r="M8" s="87" t="inlineStr">
         <is>
           <t>최경천</t>
         </is>
       </c>
-      <c r="N8" s="86" t="inlineStr">
+      <c r="N8" s="87" t="inlineStr">
         <is>
           <t>차장</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="88" t="inlineStr">
+      <c r="A9" s="89" t="inlineStr">
         <is>
           <t>강진우</t>
         </is>
       </c>
-      <c r="B9" s="86" t="inlineStr">
+      <c r="B9" s="87" t="inlineStr">
         <is>
           <t>판관</t>
         </is>
       </c>
-      <c r="C9" s="86" t="inlineStr">
+      <c r="C9" s="87" t="inlineStr">
         <is>
           <t>010-4830-8701</t>
         </is>
       </c>
-      <c r="D9" s="89" t="n">
+      <c r="D9" s="90" t="n">
         <v>153760</v>
       </c>
-      <c r="E9" s="89" t="n">
+      <c r="E9" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="90">
         <f>D9+E9</f>
         <v/>
       </c>
-      <c r="I9" s="86" t="n">
+      <c r="I9" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="86" t="inlineStr">
+      <c r="J9" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K9" s="86" t="n"/>
-      <c r="L9" s="86" t="inlineStr">
+      <c r="K9" s="87" t="n"/>
+      <c r="L9" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M9" s="86" t="inlineStr">
+      <c r="M9" s="87" t="inlineStr">
         <is>
           <t>이재선</t>
         </is>
       </c>
-      <c r="N9" s="86" t="inlineStr">
+      <c r="N9" s="87" t="inlineStr">
         <is>
           <t>차장</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="90" t="inlineStr">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>총합</t>
         </is>
       </c>
       <c r="B10" s="83" t="n"/>
-      <c r="C10" s="83" t="n"/>
-      <c r="D10" s="91">
+      <c r="C10" s="84" t="n"/>
+      <c r="D10" s="90">
         <f>SUM(D4:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="90">
         <f>SUM(E4:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="91">
+      <c r="F10" s="92">
         <f>SUM(F4:F9)</f>
         <v/>
       </c>
-      <c r="I10" s="86" t="n">
+      <c r="I10" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="86" t="inlineStr">
+      <c r="J10" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K10" s="86" t="n"/>
-      <c r="L10" s="86" t="inlineStr">
+      <c r="K10" s="87" t="n"/>
+      <c r="L10" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M10" s="86" t="inlineStr">
+      <c r="M10" s="87" t="inlineStr">
         <is>
           <t>이황</t>
         </is>
       </c>
-      <c r="N10" s="86" t="inlineStr">
+      <c r="N10" s="87" t="inlineStr">
         <is>
           <t>과장</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="I11" s="86" t="n">
+      <c r="I11" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="86" t="inlineStr">
+      <c r="J11" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K11" s="86" t="n"/>
-      <c r="L11" s="86" t="inlineStr">
+      <c r="K11" s="87" t="n"/>
+      <c r="L11" s="87" t="inlineStr">
         <is>
           <t>경영기획실</t>
         </is>
       </c>
-      <c r="M11" s="86" t="inlineStr">
+      <c r="M11" s="87" t="inlineStr">
         <is>
           <t>강소영</t>
         </is>
       </c>
-      <c r="N11" s="86" t="inlineStr">
+      <c r="N11" s="87" t="inlineStr">
         <is>
           <t>주임</t>
         </is>
@@ -4821,1050 +4859,1050 @@
         </is>
       </c>
       <c r="B12" s="83" t="n"/>
-      <c r="C12" s="83" t="n"/>
-      <c r="D12" s="84" t="n">
+      <c r="C12" s="84" t="n"/>
+      <c r="D12" s="85" t="n">
         <v>608340</v>
       </c>
-      <c r="E12" s="84" t="n">
+      <c r="E12" s="85" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="84">
+      <c r="F12" s="85">
         <f>D12+E12</f>
         <v/>
       </c>
-      <c r="I12" s="86" t="n">
+      <c r="I12" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="86" t="inlineStr">
+      <c r="J12" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K12" s="86" t="inlineStr">
+      <c r="K12" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L12" s="86" t="inlineStr">
+      <c r="L12" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="M12" s="86" t="inlineStr">
+      <c r="M12" s="87" t="inlineStr">
         <is>
           <t>오진택</t>
         </is>
       </c>
-      <c r="N12" s="86" t="inlineStr">
+      <c r="N12" s="87" t="inlineStr">
         <is>
           <t>전무</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="I13" s="86" t="n">
+      <c r="I13" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="86" t="inlineStr">
+      <c r="J13" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K13" s="86" t="inlineStr">
+      <c r="K13" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L13" s="86" t="inlineStr">
+      <c r="L13" s="87" t="inlineStr">
         <is>
           <t>설계1실</t>
         </is>
       </c>
-      <c r="M13" s="86" t="inlineStr">
+      <c r="M13" s="87" t="inlineStr">
         <is>
           <t>최우제</t>
         </is>
       </c>
-      <c r="N13" s="86" t="inlineStr">
+      <c r="N13" s="87" t="inlineStr">
         <is>
           <t>상무</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="87" t="inlineStr">
+      <c r="A14" s="88" t="inlineStr">
         <is>
           <t>성명</t>
         </is>
       </c>
-      <c r="B14" s="87" t="inlineStr">
+      <c r="B14" s="88" t="inlineStr">
         <is>
           <t>계정</t>
         </is>
       </c>
-      <c r="C14" s="87" t="inlineStr">
+      <c r="C14" s="88" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="D14" s="87" t="inlineStr">
+      <c r="D14" s="88" t="inlineStr">
         <is>
           <t>공급가</t>
         </is>
       </c>
-      <c r="E14" s="87" t="inlineStr">
+      <c r="E14" s="88" t="inlineStr">
         <is>
           <t>부가세</t>
         </is>
       </c>
-      <c r="F14" s="87" t="inlineStr">
+      <c r="F14" s="88" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="I14" s="86" t="n">
+      <c r="I14" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="86" t="inlineStr">
+      <c r="J14" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K14" s="86" t="inlineStr">
+      <c r="K14" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L14" s="86" t="inlineStr">
+      <c r="L14" s="87" t="inlineStr">
         <is>
           <t>설계1실</t>
         </is>
       </c>
-      <c r="M14" s="86" t="inlineStr">
+      <c r="M14" s="87" t="inlineStr">
         <is>
           <t>김채영</t>
         </is>
       </c>
-      <c r="N14" s="86" t="inlineStr">
+      <c r="N14" s="87" t="inlineStr">
         <is>
           <t>이사</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="88" t="inlineStr">
+      <c r="A15" s="89" t="inlineStr">
         <is>
           <t>김태우</t>
         </is>
       </c>
-      <c r="B15" s="86" t="inlineStr">
+      <c r="B15" s="87" t="inlineStr">
         <is>
           <t>판관</t>
         </is>
       </c>
-      <c r="C15" s="86" t="inlineStr">
+      <c r="C15" s="87" t="inlineStr">
         <is>
           <t>010-8509-5339</t>
         </is>
       </c>
-      <c r="D15" s="89" t="n">
+      <c r="D15" s="90" t="n">
         <v>101060</v>
       </c>
-      <c r="E15" s="89" t="n">
+      <c r="E15" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="90">
         <f>D15+E15</f>
         <v/>
       </c>
-      <c r="I15" s="86" t="n">
+      <c r="I15" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="86" t="inlineStr">
+      <c r="J15" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K15" s="86" t="inlineStr">
+      <c r="K15" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L15" s="86" t="inlineStr">
+      <c r="L15" s="87" t="inlineStr">
         <is>
           <t>설계1실</t>
         </is>
       </c>
-      <c r="M15" s="86" t="inlineStr">
+      <c r="M15" s="87" t="inlineStr">
         <is>
           <t>김태은</t>
         </is>
       </c>
-      <c r="N15" s="86" t="inlineStr">
+      <c r="N15" s="87" t="inlineStr">
         <is>
           <t>과장</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="88" t="inlineStr">
+      <c r="A16" s="89" t="inlineStr">
         <is>
           <t>김갑득</t>
         </is>
       </c>
-      <c r="B16" s="86" t="inlineStr">
+      <c r="B16" s="87" t="inlineStr">
         <is>
           <t>연구</t>
         </is>
       </c>
-      <c r="C16" s="86" t="inlineStr">
+      <c r="C16" s="87" t="inlineStr">
         <is>
           <t>010-9751-1800</t>
         </is>
       </c>
-      <c r="D16" s="89" t="n">
+      <c r="D16" s="90" t="n">
         <v>94940</v>
       </c>
-      <c r="E16" s="89" t="n">
+      <c r="E16" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="90">
         <f>D16+E16</f>
         <v/>
       </c>
-      <c r="I16" s="86" t="n">
+      <c r="I16" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="86" t="inlineStr">
+      <c r="J16" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K16" s="86" t="inlineStr">
+      <c r="K16" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L16" s="86" t="inlineStr">
+      <c r="L16" s="87" t="inlineStr">
         <is>
           <t>설계1실</t>
         </is>
       </c>
-      <c r="M16" s="86" t="inlineStr">
+      <c r="M16" s="87" t="inlineStr">
         <is>
           <t>기재관</t>
         </is>
       </c>
-      <c r="N16" s="86" t="inlineStr">
+      <c r="N16" s="87" t="inlineStr">
         <is>
           <t>과장</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="inlineStr">
+      <c r="A17" s="89" t="inlineStr">
         <is>
           <t>조재준</t>
         </is>
       </c>
-      <c r="B17" s="86" t="inlineStr">
+      <c r="B17" s="87" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C17" s="86" t="inlineStr">
+      <c r="C17" s="87" t="inlineStr">
         <is>
           <t>010-2626-4326</t>
         </is>
       </c>
-      <c r="D17" s="89" t="n">
+      <c r="D17" s="90" t="n">
         <v>52340</v>
       </c>
-      <c r="E17" s="89" t="n">
+      <c r="E17" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="89">
+      <c r="F17" s="90">
         <f>D17+E17</f>
         <v/>
       </c>
-      <c r="I17" s="86" t="n">
+      <c r="I17" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="J17" s="86" t="inlineStr">
+      <c r="J17" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K17" s="86" t="inlineStr">
+      <c r="K17" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L17" s="86" t="inlineStr">
+      <c r="L17" s="87" t="inlineStr">
         <is>
           <t>설계1실</t>
         </is>
       </c>
-      <c r="M17" s="86" t="inlineStr">
+      <c r="M17" s="87" t="inlineStr">
         <is>
           <t>김민호</t>
         </is>
       </c>
-      <c r="N17" s="86" t="inlineStr">
+      <c r="N17" s="87" t="inlineStr">
         <is>
           <t>대리</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="88" t="inlineStr">
+      <c r="A18" s="89" t="inlineStr">
         <is>
           <t>최진달미</t>
         </is>
       </c>
-      <c r="B18" s="86" t="inlineStr">
+      <c r="B18" s="87" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C18" s="86" t="inlineStr">
+      <c r="C18" s="87" t="inlineStr">
         <is>
           <t>010-3712-5165</t>
         </is>
       </c>
-      <c r="D18" s="89" t="n">
+      <c r="D18" s="90" t="n">
         <v>65520</v>
       </c>
-      <c r="E18" s="89" t="n">
+      <c r="E18" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="89">
+      <c r="F18" s="90">
         <f>D18+E18</f>
         <v/>
       </c>
-      <c r="I18" s="86" t="n">
+      <c r="I18" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="J18" s="86" t="inlineStr">
+      <c r="J18" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K18" s="86" t="inlineStr">
+      <c r="K18" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L18" s="86" t="inlineStr">
+      <c r="L18" s="87" t="inlineStr">
         <is>
           <t>설계1실</t>
         </is>
       </c>
-      <c r="M18" s="86" t="inlineStr">
+      <c r="M18" s="87" t="inlineStr">
         <is>
           <t>이수영</t>
         </is>
       </c>
-      <c r="N18" s="86" t="inlineStr">
+      <c r="N18" s="87" t="inlineStr">
         <is>
           <t>주임</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="88" t="inlineStr">
+      <c r="A19" s="89" t="inlineStr">
         <is>
           <t>최대현</t>
         </is>
       </c>
-      <c r="B19" s="86" t="inlineStr">
+      <c r="B19" s="87" t="inlineStr">
         <is>
           <t>제조</t>
         </is>
       </c>
-      <c r="C19" s="86" t="inlineStr">
+      <c r="C19" s="87" t="inlineStr">
         <is>
           <t>010-2266-1712</t>
         </is>
       </c>
-      <c r="D19" s="89" t="n">
+      <c r="D19" s="90" t="n">
         <v>155210</v>
       </c>
-      <c r="E19" s="89" t="n">
+      <c r="E19" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="89">
+      <c r="F19" s="90">
         <f>D19+E19</f>
         <v/>
       </c>
-      <c r="I19" s="86" t="n">
+      <c r="I19" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="J19" s="86" t="inlineStr">
+      <c r="J19" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K19" s="86" t="inlineStr">
+      <c r="K19" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L19" s="86" t="inlineStr">
+      <c r="L19" s="87" t="inlineStr">
         <is>
           <t>설계1실</t>
         </is>
       </c>
-      <c r="M19" s="86" t="inlineStr">
+      <c r="M19" s="87" t="inlineStr">
         <is>
           <t>최수용</t>
         </is>
       </c>
-      <c r="N19" s="86" t="inlineStr">
+      <c r="N19" s="87" t="inlineStr">
         <is>
           <t>사원</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="88" t="inlineStr">
+      <c r="A20" s="89" t="inlineStr">
         <is>
           <t>김명진</t>
         </is>
       </c>
-      <c r="B20" s="86" t="inlineStr">
+      <c r="B20" s="87" t="inlineStr">
         <is>
           <t>판관</t>
         </is>
       </c>
-      <c r="C20" s="86" t="inlineStr">
+      <c r="C20" s="87" t="inlineStr">
         <is>
           <t>010-9443-0907</t>
         </is>
       </c>
-      <c r="D20" s="89" t="n">
+      <c r="D20" s="90" t="n">
         <v>139270</v>
       </c>
-      <c r="E20" s="89" t="n">
+      <c r="E20" s="90" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="89">
+      <c r="F20" s="90">
         <f>D20+E20</f>
         <v/>
       </c>
-      <c r="I20" s="86" t="n">
+      <c r="I20" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="86" t="inlineStr">
+      <c r="J20" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K20" s="86" t="inlineStr">
+      <c r="K20" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L20" s="86" t="inlineStr">
+      <c r="L20" s="87" t="inlineStr">
         <is>
           <t>설계2실</t>
         </is>
       </c>
-      <c r="M20" s="86" t="inlineStr">
+      <c r="M20" s="87" t="inlineStr">
         <is>
           <t>조지은</t>
         </is>
       </c>
-      <c r="N20" s="86" t="inlineStr">
+      <c r="N20" s="87" t="inlineStr">
         <is>
           <t>이사</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="90" t="inlineStr">
+      <c r="A21" s="91" t="inlineStr">
         <is>
           <t>총합</t>
         </is>
       </c>
       <c r="B21" s="83" t="n"/>
-      <c r="C21" s="83" t="n"/>
-      <c r="D21" s="91">
+      <c r="C21" s="84" t="n"/>
+      <c r="D21" s="90">
         <f>SUM(D15:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="91">
+      <c r="E21" s="90">
         <f>SUM(E15:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="91">
+      <c r="F21" s="92">
         <f>SUM(F15:F20)</f>
         <v/>
       </c>
-      <c r="I21" s="86" t="n">
+      <c r="I21" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="J21" s="86" t="inlineStr">
+      <c r="J21" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K21" s="86" t="inlineStr">
+      <c r="K21" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L21" s="86" t="inlineStr">
+      <c r="L21" s="87" t="inlineStr">
         <is>
           <t>설계2실</t>
         </is>
       </c>
-      <c r="M21" s="86" t="inlineStr">
+      <c r="M21" s="87" t="inlineStr">
         <is>
           <t>이예솔</t>
         </is>
       </c>
-      <c r="N21" s="86" t="inlineStr">
+      <c r="N21" s="87" t="inlineStr">
         <is>
           <t>과장</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="I22" s="86" t="n">
+      <c r="I22" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="86" t="inlineStr">
+      <c r="J22" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K22" s="86" t="inlineStr">
+      <c r="K22" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L22" s="86" t="inlineStr">
+      <c r="L22" s="87" t="inlineStr">
         <is>
           <t>설계2실</t>
         </is>
       </c>
-      <c r="M22" s="86" t="inlineStr">
+      <c r="M22" s="87" t="inlineStr">
         <is>
           <t>류승호</t>
         </is>
       </c>
-      <c r="N22" s="86" t="inlineStr">
+      <c r="N22" s="87" t="inlineStr">
         <is>
           <t>과장</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="I23" s="86" t="n">
+      <c r="I23" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="J23" s="86" t="inlineStr">
+      <c r="J23" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K23" s="86" t="inlineStr">
+      <c r="K23" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L23" s="86" t="inlineStr">
+      <c r="L23" s="87" t="inlineStr">
         <is>
           <t>설계2실</t>
         </is>
       </c>
-      <c r="M23" s="86" t="inlineStr">
+      <c r="M23" s="87" t="inlineStr">
         <is>
           <t>최수지</t>
         </is>
       </c>
-      <c r="N23" s="86" t="inlineStr">
+      <c r="N23" s="87" t="inlineStr">
         <is>
           <t>과장</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="I24" s="86" t="n">
+      <c r="I24" s="87" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="86" t="inlineStr">
+      <c r="J24" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K24" s="86" t="inlineStr">
+      <c r="K24" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L24" s="86" t="inlineStr">
+      <c r="L24" s="87" t="inlineStr">
         <is>
           <t>설계2실</t>
         </is>
       </c>
-      <c r="M24" s="86" t="inlineStr">
+      <c r="M24" s="87" t="inlineStr">
         <is>
           <t>황진욱</t>
         </is>
       </c>
-      <c r="N24" s="86" t="inlineStr">
+      <c r="N24" s="87" t="inlineStr">
         <is>
           <t>대리</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="I25" s="86" t="n">
+      <c r="I25" s="87" t="n">
         <v>14</v>
       </c>
-      <c r="J25" s="86" t="inlineStr">
+      <c r="J25" s="87" t="inlineStr">
         <is>
           <t>6층</t>
         </is>
       </c>
-      <c r="K25" s="86" t="inlineStr">
+      <c r="K25" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L25" s="86" t="inlineStr">
+      <c r="L25" s="87" t="inlineStr">
         <is>
           <t>설계2실</t>
         </is>
       </c>
-      <c r="M25" s="86" t="inlineStr">
+      <c r="M25" s="87" t="inlineStr">
         <is>
           <t>오한솔</t>
         </is>
       </c>
-      <c r="N25" s="86" t="inlineStr">
+      <c r="N25" s="87" t="inlineStr">
         <is>
           <t>주임</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="I26" s="86" t="n">
+      <c r="I26" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="86" t="inlineStr">
+      <c r="J26" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K26" s="86" t="inlineStr">
+      <c r="K26" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L26" s="86" t="inlineStr">
+      <c r="L26" s="87" t="inlineStr">
         <is>
           <t>신사업개발실</t>
         </is>
       </c>
-      <c r="M26" s="86" t="inlineStr">
+      <c r="M26" s="87" t="inlineStr">
         <is>
           <t>최진달미</t>
         </is>
       </c>
-      <c r="N26" s="86" t="inlineStr">
+      <c r="N26" s="87" t="inlineStr">
         <is>
           <t>전무</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="I27" s="86" t="n">
+      <c r="I27" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="86" t="inlineStr">
+      <c r="J27" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K27" s="86" t="inlineStr">
+      <c r="K27" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L27" s="86" t="inlineStr">
+      <c r="L27" s="87" t="inlineStr">
         <is>
           <t>신사업개발실</t>
         </is>
       </c>
-      <c r="M27" s="86" t="inlineStr">
+      <c r="M27" s="87" t="inlineStr">
         <is>
           <t>박종철</t>
         </is>
       </c>
-      <c r="N27" s="86" t="inlineStr">
+      <c r="N27" s="87" t="inlineStr">
         <is>
           <t>이사</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="I28" s="86" t="n">
+      <c r="I28" s="87" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="86" t="inlineStr">
+      <c r="J28" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K28" s="86" t="inlineStr">
+      <c r="K28" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L28" s="86" t="inlineStr">
+      <c r="L28" s="87" t="inlineStr">
         <is>
           <t>신사업개발실</t>
         </is>
       </c>
-      <c r="M28" s="86" t="inlineStr">
+      <c r="M28" s="87" t="inlineStr">
         <is>
           <t>이정진</t>
         </is>
       </c>
-      <c r="N28" s="86" t="inlineStr">
+      <c r="N28" s="87" t="inlineStr">
         <is>
           <t>부장</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="I29" s="86" t="n">
+      <c r="I29" s="87" t="n">
         <v>4</v>
       </c>
-      <c r="J29" s="86" t="inlineStr">
+      <c r="J29" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K29" s="86" t="inlineStr">
+      <c r="K29" s="87" t="inlineStr">
         <is>
           <t>설계본부</t>
         </is>
       </c>
-      <c r="L29" s="86" t="inlineStr">
+      <c r="L29" s="87" t="inlineStr">
         <is>
           <t>신사업개발실</t>
         </is>
       </c>
-      <c r="M29" s="86" t="inlineStr">
+      <c r="M29" s="87" t="inlineStr">
         <is>
           <t>김순성</t>
         </is>
       </c>
-      <c r="N29" s="86" t="inlineStr">
+      <c r="N29" s="87" t="inlineStr">
         <is>
           <t>고문</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="I30" s="86" t="n">
+      <c r="I30" s="87" t="n">
         <v>5</v>
       </c>
-      <c r="J30" s="86" t="inlineStr">
+      <c r="J30" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K30" s="86" t="inlineStr">
+      <c r="K30" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L30" s="86" t="inlineStr">
+      <c r="L30" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="M30" s="86" t="inlineStr">
+      <c r="M30" s="87" t="inlineStr">
         <is>
           <t>김동우</t>
         </is>
       </c>
-      <c r="N30" s="86" t="inlineStr">
+      <c r="N30" s="87" t="inlineStr">
         <is>
           <t>전무</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="I31" s="86" t="n">
+      <c r="I31" s="87" t="n">
         <v>6</v>
       </c>
-      <c r="J31" s="86" t="inlineStr">
+      <c r="J31" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K31" s="86" t="inlineStr">
+      <c r="K31" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L31" s="86" t="inlineStr">
+      <c r="L31" s="87" t="inlineStr">
         <is>
           <t>사업관리실</t>
         </is>
       </c>
-      <c r="M31" s="86" t="inlineStr">
+      <c r="M31" s="87" t="inlineStr">
         <is>
           <t>이성규</t>
         </is>
       </c>
-      <c r="N31" s="86" t="inlineStr">
+      <c r="N31" s="87" t="inlineStr">
         <is>
           <t>차장</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="I32" s="86" t="n">
+      <c r="I32" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="J32" s="86" t="inlineStr">
+      <c r="J32" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K32" s="86" t="inlineStr">
+      <c r="K32" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L32" s="86" t="inlineStr">
+      <c r="L32" s="87" t="inlineStr">
         <is>
           <t>사업관리실</t>
         </is>
       </c>
-      <c r="M32" s="86" t="inlineStr">
+      <c r="M32" s="87" t="inlineStr">
         <is>
           <t>이강호</t>
         </is>
       </c>
-      <c r="N32" s="86" t="inlineStr">
+      <c r="N32" s="87" t="inlineStr">
         <is>
           <t>차장</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="I33" s="86" t="n">
+      <c r="I33" s="87" t="n">
         <v>8</v>
       </c>
-      <c r="J33" s="86" t="inlineStr">
+      <c r="J33" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K33" s="86" t="inlineStr">
+      <c r="K33" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L33" s="86" t="inlineStr">
+      <c r="L33" s="87" t="inlineStr">
         <is>
           <t>사업관리실</t>
         </is>
       </c>
-      <c r="M33" s="86" t="inlineStr">
+      <c r="M33" s="87" t="inlineStr">
         <is>
           <t>김동규</t>
         </is>
       </c>
-      <c r="N33" s="86" t="inlineStr">
+      <c r="N33" s="87" t="inlineStr">
         <is>
           <t>부장</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="I34" s="86" t="n">
+      <c r="I34" s="87" t="n">
         <v>9</v>
       </c>
-      <c r="J34" s="86" t="inlineStr">
+      <c r="J34" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K34" s="86" t="inlineStr">
+      <c r="K34" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L34" s="86" t="inlineStr">
+      <c r="L34" s="87" t="inlineStr">
         <is>
           <t>사업관리실</t>
         </is>
       </c>
-      <c r="M34" s="86" t="inlineStr">
+      <c r="M34" s="87" t="inlineStr">
         <is>
           <t>이완구</t>
         </is>
       </c>
-      <c r="N34" s="86" t="inlineStr">
+      <c r="N34" s="87" t="inlineStr">
         <is>
           <t>부장</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="I35" s="86" t="n">
+      <c r="I35" s="87" t="n">
         <v>10</v>
       </c>
-      <c r="J35" s="86" t="inlineStr">
+      <c r="J35" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K35" s="86" t="inlineStr">
+      <c r="K35" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L35" s="86" t="inlineStr">
+      <c r="L35" s="87" t="inlineStr">
         <is>
           <t>영업관리실</t>
         </is>
       </c>
-      <c r="M35" s="86" t="inlineStr">
+      <c r="M35" s="87" t="inlineStr">
         <is>
           <t>주현철</t>
         </is>
       </c>
-      <c r="N35" s="86" t="inlineStr">
+      <c r="N35" s="87" t="inlineStr">
         <is>
           <t>상무</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="I36" s="86" t="n">
+      <c r="I36" s="87" t="n">
         <v>11</v>
       </c>
-      <c r="J36" s="86" t="inlineStr">
+      <c r="J36" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K36" s="86" t="inlineStr">
+      <c r="K36" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L36" s="86" t="inlineStr">
+      <c r="L36" s="87" t="inlineStr">
         <is>
           <t>영업관리실</t>
         </is>
       </c>
-      <c r="M36" s="86" t="inlineStr">
+      <c r="M36" s="87" t="inlineStr">
         <is>
           <t>문광정</t>
         </is>
       </c>
-      <c r="N36" s="86" t="inlineStr">
+      <c r="N36" s="87" t="inlineStr">
         <is>
           <t>부장</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="I37" s="86" t="n">
+      <c r="I37" s="87" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="86" t="inlineStr">
+      <c r="J37" s="87" t="inlineStr">
         <is>
           <t>13층</t>
         </is>
       </c>
-      <c r="K37" s="86" t="inlineStr">
+      <c r="K37" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L37" s="86" t="inlineStr">
+      <c r="L37" s="87" t="inlineStr">
         <is>
           <t>영업관리실</t>
         </is>
       </c>
-      <c r="M37" s="86" t="inlineStr">
+      <c r="M37" s="87" t="inlineStr">
         <is>
           <t>이현섭</t>
         </is>
       </c>
-      <c r="N37" s="86" t="inlineStr">
+      <c r="N37" s="87" t="inlineStr">
         <is>
           <t>주임</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="I38" s="86" t="n">
+      <c r="I38" s="87" t="n">
         <v>13</v>
       </c>
-      <c r="J38" s="86" t="inlineStr">
+      <c r="J38" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K38" s="86" t="inlineStr">
+      <c r="K38" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L38" s="86" t="inlineStr">
+      <c r="L38" s="87" t="inlineStr">
         <is>
           <t>영업관리실</t>
         </is>
       </c>
-      <c r="M38" s="86" t="inlineStr">
+      <c r="M38" s="87" t="inlineStr">
         <is>
           <t>김진규</t>
         </is>
       </c>
-      <c r="N38" s="86" t="inlineStr">
+      <c r="N38" s="87" t="inlineStr">
         <is>
           <t>대리</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="I39" s="86" t="n">
+      <c r="I39" s="87" t="n">
         <v>14</v>
       </c>
-      <c r="J39" s="86" t="inlineStr">
+      <c r="J39" s="87" t="inlineStr">
         <is>
           <t>11층</t>
         </is>
       </c>
-      <c r="K39" s="86" t="inlineStr">
+      <c r="K39" s="87" t="inlineStr">
         <is>
           <t>사업관리본부</t>
         </is>
       </c>
-      <c r="L39" s="86" t="inlineStr">
+      <c r="L39" s="87" t="inlineStr">
         <is>
           <t>영업관리실</t>
         </is>
       </c>
-      <c r="M39" s="86" t="inlineStr">
+      <c r="M39" s="87" t="inlineStr">
         <is>
           <t>연지현</t>
         </is>
       </c>
-      <c r="N39" s="86" t="inlineStr">
+      <c r="N39" s="87" t="inlineStr">
         <is>
           <t>주임</t>
         </is>
@@ -5873,15 +5911,1657 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.375" customWidth="1" style="53" min="1" max="1"/>
+    <col width="10.75" customWidth="1" style="53" min="2" max="2"/>
+    <col width="8.125" customWidth="1" style="53" min="3" max="3"/>
+    <col width="12.875" customWidth="1" style="53" min="4" max="4"/>
+    <col width="16.75" customWidth="1" style="53" min="5" max="5"/>
+    <col width="15.25" customWidth="1" style="53" min="6" max="6"/>
+    <col width="2" customWidth="1" style="53" min="7" max="7"/>
+    <col width="2" customWidth="1" style="53" min="8" max="8"/>
+    <col width="9" customWidth="1" style="53" min="9" max="9"/>
+    <col width="7" customWidth="1" style="53" min="10" max="10"/>
+    <col width="11.375" customWidth="1" style="53" min="11" max="11"/>
+    <col width="12.75" customWidth="1" style="53" min="12" max="12"/>
+    <col width="9" customWidth="1" style="53" min="13" max="13"/>
+    <col width="9" customWidth="1" style="53" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="I1" s="86" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="J1" s="86" t="inlineStr">
+        <is>
+          <t>층</t>
+        </is>
+      </c>
+      <c r="K1" s="86" t="inlineStr">
+        <is>
+          <t>부서명(본부)</t>
+        </is>
+      </c>
+      <c r="L1" s="86" t="inlineStr">
+        <is>
+          <t>부서명(실이하)</t>
+        </is>
+      </c>
+      <c r="M1" s="86" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="N1" s="86" t="inlineStr">
+        <is>
+          <t>직위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="82" t="inlineStr">
+        <is>
+          <t>인터넷통신비 총액(6층)</t>
+        </is>
+      </c>
+      <c r="B2" s="83" t="n"/>
+      <c r="C2" s="84" t="n"/>
+      <c r="D2" s="85" t="n">
+        <v>88525</v>
+      </c>
+      <c r="E2" s="85" t="n">
+        <v>8852</v>
+      </c>
+      <c r="F2" s="85">
+        <f>D2+E2</f>
+        <v/>
+      </c>
+      <c r="I2" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K2" s="87" t="inlineStr">
+        <is>
+          <t>감사역</t>
+        </is>
+      </c>
+      <c r="L2" s="87" t="inlineStr">
+        <is>
+          <t>감사역</t>
+        </is>
+      </c>
+      <c r="M2" s="87" t="inlineStr">
+        <is>
+          <t>김태우</t>
+        </is>
+      </c>
+      <c r="N2" s="87" t="inlineStr">
+        <is>
+          <t>상무</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="I3" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K3" s="87" t="inlineStr">
+        <is>
+          <t>R&amp;D본부</t>
+        </is>
+      </c>
+      <c r="L3" s="87" t="inlineStr">
+        <is>
+          <t>R&amp;D본부</t>
+        </is>
+      </c>
+      <c r="M3" s="87" t="inlineStr">
+        <is>
+          <t>김갑득</t>
+        </is>
+      </c>
+      <c r="N3" s="87" t="inlineStr">
+        <is>
+          <t>사장</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="88" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="B4" s="88" t="inlineStr">
+        <is>
+          <t>계정</t>
+        </is>
+      </c>
+      <c r="C4" s="88" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="D4" s="88" t="inlineStr">
+        <is>
+          <t>공급가</t>
+        </is>
+      </c>
+      <c r="E4" s="88" t="inlineStr">
+        <is>
+          <t>부가세</t>
+        </is>
+      </c>
+      <c r="F4" s="88" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="I4" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K4" s="87" t="n"/>
+      <c r="L4" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M4" s="87" t="inlineStr">
+        <is>
+          <t>김명진</t>
+        </is>
+      </c>
+      <c r="N4" s="87" t="inlineStr">
+        <is>
+          <t>상무</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="89" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="C5" s="93">
+        <f>COUNTIF(L:L,"설계1실")</f>
+        <v/>
+      </c>
+      <c r="D5" s="90">
+        <f>ROUND($D$2/$C$8*C5,0)</f>
+        <v/>
+      </c>
+      <c r="E5" s="90">
+        <f>ROUND($E$2/$C$8*C5,0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="90">
+        <f>D5+E5</f>
+        <v/>
+      </c>
+      <c r="I5" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K5" s="87" t="n"/>
+      <c r="L5" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M5" s="87" t="inlineStr">
+        <is>
+          <t>이재영</t>
+        </is>
+      </c>
+      <c r="N5" s="87" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>설계2실</t>
+        </is>
+      </c>
+      <c r="B6" s="87" t="inlineStr">
+        <is>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="C6" s="93">
+        <f>COUNTIF(L:L,"설계2실")</f>
+        <v/>
+      </c>
+      <c r="D6" s="90">
+        <f>ROUND($D$2/$C$8*C6,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="90">
+        <f>ROUND($E$2/$C$8*C6,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="90">
+        <f>D6+E6</f>
+        <v/>
+      </c>
+      <c r="I6" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K6" s="87" t="n"/>
+      <c r="L6" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M6" s="87" t="inlineStr">
+        <is>
+          <t>강지혜</t>
+        </is>
+      </c>
+      <c r="N6" s="87" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="89" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="C7" s="93">
+        <f>COUNTIF(L:L,"설계본부")</f>
+        <v/>
+      </c>
+      <c r="D7" s="90">
+        <f>ROUND($D$2/$C$8*C7,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="90">
+        <f>ROUND($E$2/$C$8*C7,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="90">
+        <f>D7+E7</f>
+        <v/>
+      </c>
+      <c r="I7" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K7" s="87" t="n"/>
+      <c r="L7" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M7" s="87" t="inlineStr">
+        <is>
+          <t>이경태</t>
+        </is>
+      </c>
+      <c r="N7" s="87" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="91" t="inlineStr">
+        <is>
+          <t>총합</t>
+        </is>
+      </c>
+      <c r="B8" s="94" t="n"/>
+      <c r="C8" s="93">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="90">
+        <f>SUM(D5:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="90">
+        <f>SUM(E5:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="92">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K8" s="87" t="n"/>
+      <c r="L8" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M8" s="87" t="inlineStr">
+        <is>
+          <t>최경천</t>
+        </is>
+      </c>
+      <c r="N8" s="87" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="I9" s="87" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K9" s="87" t="n"/>
+      <c r="L9" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M9" s="87" t="inlineStr">
+        <is>
+          <t>이재선</t>
+        </is>
+      </c>
+      <c r="N9" s="87" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>인터넷통신비 총액(11층)</t>
+        </is>
+      </c>
+      <c r="B10" s="83" t="n"/>
+      <c r="C10" s="84" t="n"/>
+      <c r="D10" s="85" t="n">
+        <v>88525</v>
+      </c>
+      <c r="E10" s="85" t="n">
+        <v>8852</v>
+      </c>
+      <c r="F10" s="85">
+        <f>D10+E10</f>
+        <v/>
+      </c>
+      <c r="I10" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K10" s="87" t="n"/>
+      <c r="L10" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M10" s="87" t="inlineStr">
+        <is>
+          <t>이황</t>
+        </is>
+      </c>
+      <c r="N10" s="87" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="I11" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K11" s="87" t="n"/>
+      <c r="L11" s="87" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="M11" s="87" t="inlineStr">
+        <is>
+          <t>강소영</t>
+        </is>
+      </c>
+      <c r="N11" s="87" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="88" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="B12" s="88" t="inlineStr">
+        <is>
+          <t>계정</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="D12" s="88" t="inlineStr">
+        <is>
+          <t>공급가</t>
+        </is>
+      </c>
+      <c r="E12" s="88" t="inlineStr">
+        <is>
+          <t>부가세</t>
+        </is>
+      </c>
+      <c r="F12" s="88" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="I12" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K12" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L12" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="M12" s="87" t="inlineStr">
+        <is>
+          <t>오진택</t>
+        </is>
+      </c>
+      <c r="N12" s="87" t="inlineStr">
+        <is>
+          <t>전무</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="89" t="inlineStr">
+        <is>
+          <t>신사업개발실</t>
+        </is>
+      </c>
+      <c r="B13" s="87" t="inlineStr">
+        <is>
+          <t>제조</t>
+        </is>
+      </c>
+      <c r="C13" s="93">
+        <f>COUNTIF(L:L,"신사업개발실")</f>
+        <v/>
+      </c>
+      <c r="D13" s="90">
+        <f>ROUND($D$10/$C$17*C13,0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="90">
+        <f>ROUND($E$10/$C$17*C13,0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="90">
+        <f>D13+E13</f>
+        <v/>
+      </c>
+      <c r="I13" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K13" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L13" s="87" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="M13" s="87" t="inlineStr">
+        <is>
+          <t>최우제</t>
+        </is>
+      </c>
+      <c r="N13" s="87" t="inlineStr">
+        <is>
+          <t>상무</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="89" t="inlineStr">
+        <is>
+          <t>영업관리실</t>
+        </is>
+      </c>
+      <c r="B14" s="87" t="inlineStr">
+        <is>
+          <t>판관</t>
+        </is>
+      </c>
+      <c r="C14" s="93">
+        <f>COUNTIF(L:L,"영업관리실")</f>
+        <v/>
+      </c>
+      <c r="D14" s="90">
+        <f>ROUND($D$10/$C$17*C14,0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="90">
+        <f>ROUND($E$10/$C$17*C14,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="90">
+        <f>D14+E14</f>
+        <v/>
+      </c>
+      <c r="I14" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K14" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L14" s="87" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="M14" s="87" t="inlineStr">
+        <is>
+          <t>김채영</t>
+        </is>
+      </c>
+      <c r="N14" s="87" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="89" t="inlineStr">
+        <is>
+          <t>사업관리실</t>
+        </is>
+      </c>
+      <c r="B15" s="87" t="inlineStr">
+        <is>
+          <t>판관</t>
+        </is>
+      </c>
+      <c r="C15" s="93">
+        <f>COUNTIF(L:L,"사업관리실")</f>
+        <v/>
+      </c>
+      <c r="D15" s="90">
+        <f>ROUND($D$10/$C$17*C15,0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="90">
+        <f>ROUND($E$10/$C$17*C15,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="90">
+        <f>D15+E15</f>
+        <v/>
+      </c>
+      <c r="I15" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K15" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L15" s="87" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="M15" s="87" t="inlineStr">
+        <is>
+          <t>김태은</t>
+        </is>
+      </c>
+      <c r="N15" s="87" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="89" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="B16" s="87" t="inlineStr">
+        <is>
+          <t>판관</t>
+        </is>
+      </c>
+      <c r="C16" s="93">
+        <f>COUNTIF(L:L,"사업관리본부")</f>
+        <v/>
+      </c>
+      <c r="D16" s="90">
+        <f>ROUND($D$10/$C$17*C16,0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="90">
+        <f>ROUND($E$10/$C$17*C16,0)+1</f>
+        <v/>
+      </c>
+      <c r="F16" s="90">
+        <f>D16+E16</f>
+        <v/>
+      </c>
+      <c r="I16" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K16" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L16" s="87" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="M16" s="87" t="inlineStr">
+        <is>
+          <t>기재관</t>
+        </is>
+      </c>
+      <c r="N16" s="87" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="91" t="inlineStr">
+        <is>
+          <t>총합</t>
+        </is>
+      </c>
+      <c r="B17" s="94" t="n"/>
+      <c r="C17" s="93">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="90">
+        <f>SUM(D13:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="90">
+        <f>SUM(E13:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="92">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K17" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L17" s="87" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="M17" s="87" t="inlineStr">
+        <is>
+          <t>김민호</t>
+        </is>
+      </c>
+      <c r="N17" s="87" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K18" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L18" s="87" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="M18" s="87" t="inlineStr">
+        <is>
+          <t>이수영</t>
+        </is>
+      </c>
+      <c r="N18" s="87" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="82" t="inlineStr">
+        <is>
+          <t>인터넷통신비 총액(13층)</t>
+        </is>
+      </c>
+      <c r="B19" s="83" t="n"/>
+      <c r="C19" s="84" t="n"/>
+      <c r="D19" s="85" t="n">
+        <v>63232</v>
+      </c>
+      <c r="E19" s="85" t="n">
+        <v>6324</v>
+      </c>
+      <c r="F19" s="85">
+        <f>D19+E19</f>
+        <v/>
+      </c>
+      <c r="I19" s="87" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K19" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L19" s="87" t="inlineStr">
+        <is>
+          <t>설계1실</t>
+        </is>
+      </c>
+      <c r="M19" s="87" t="inlineStr">
+        <is>
+          <t>최수용</t>
+        </is>
+      </c>
+      <c r="N19" s="87" t="inlineStr">
+        <is>
+          <t>사원</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K20" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L20" s="87" t="inlineStr">
+        <is>
+          <t>설계2실</t>
+        </is>
+      </c>
+      <c r="M20" s="87" t="inlineStr">
+        <is>
+          <t>조지은</t>
+        </is>
+      </c>
+      <c r="N20" s="87" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="88" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="B21" s="88" t="inlineStr">
+        <is>
+          <t>계정</t>
+        </is>
+      </c>
+      <c r="C21" s="88" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="D21" s="88" t="inlineStr">
+        <is>
+          <t>공급가</t>
+        </is>
+      </c>
+      <c r="E21" s="88" t="inlineStr">
+        <is>
+          <t>부가세</t>
+        </is>
+      </c>
+      <c r="F21" s="88" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="I21" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K21" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L21" s="87" t="inlineStr">
+        <is>
+          <t>설계2실</t>
+        </is>
+      </c>
+      <c r="M21" s="87" t="inlineStr">
+        <is>
+          <t>이예솔</t>
+        </is>
+      </c>
+      <c r="N21" s="87" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="89" t="inlineStr">
+        <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="B22" s="87" t="inlineStr">
+        <is>
+          <t>판관</t>
+        </is>
+      </c>
+      <c r="C22" s="93">
+        <f>COUNTIF(L:L,"경영기획실")</f>
+        <v/>
+      </c>
+      <c r="D22" s="90">
+        <f>ROUND($D$19/$C$25*C22,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="90">
+        <f>ROUND($E$19/$C$25*C22,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="90">
+        <f>D22+E22</f>
+        <v/>
+      </c>
+      <c r="I22" s="87" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K22" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L22" s="87" t="inlineStr">
+        <is>
+          <t>설계2실</t>
+        </is>
+      </c>
+      <c r="M22" s="87" t="inlineStr">
+        <is>
+          <t>류승호</t>
+        </is>
+      </c>
+      <c r="N22" s="87" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="89" t="inlineStr">
+        <is>
+          <t>감사역</t>
+        </is>
+      </c>
+      <c r="B23" s="87" t="inlineStr">
+        <is>
+          <t>판관</t>
+        </is>
+      </c>
+      <c r="C23" s="93">
+        <f>COUNTIF(L:L,"감사역")</f>
+        <v/>
+      </c>
+      <c r="D23" s="90">
+        <f>ROUND($D$19/$C$25*C23,0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="90">
+        <f>ROUND($E$19/$C$25*C23,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="90">
+        <f>D23+E23</f>
+        <v/>
+      </c>
+      <c r="I23" s="87" t="n">
+        <v>12</v>
+      </c>
+      <c r="J23" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K23" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L23" s="87" t="inlineStr">
+        <is>
+          <t>설계2실</t>
+        </is>
+      </c>
+      <c r="M23" s="87" t="inlineStr">
+        <is>
+          <t>최수지</t>
+        </is>
+      </c>
+      <c r="N23" s="87" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="89" t="inlineStr">
+        <is>
+          <t>R&amp;D본부</t>
+        </is>
+      </c>
+      <c r="B24" s="87" t="inlineStr">
+        <is>
+          <t>연구</t>
+        </is>
+      </c>
+      <c r="C24" s="93">
+        <f>COUNTIF(L:L,"R&amp;D본부")</f>
+        <v/>
+      </c>
+      <c r="D24" s="90">
+        <f>ROUND($D$19/$C$25*C24,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="90">
+        <f>ROUND($E$19/$C$25*C24,0)+1</f>
+        <v/>
+      </c>
+      <c r="F24" s="90">
+        <f>D24+E24</f>
+        <v/>
+      </c>
+      <c r="I24" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K24" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L24" s="87" t="inlineStr">
+        <is>
+          <t>설계2실</t>
+        </is>
+      </c>
+      <c r="M24" s="87" t="inlineStr">
+        <is>
+          <t>황진욱</t>
+        </is>
+      </c>
+      <c r="N24" s="87" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>총합</t>
+        </is>
+      </c>
+      <c r="B25" s="94" t="n"/>
+      <c r="C25" s="93">
+        <f>SUM(C22:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="90">
+        <f>SUM(D22:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="90">
+        <f>SUM(E22:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="92">
+        <f>SUM(F22:F24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="87" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" s="87" t="inlineStr">
+        <is>
+          <t>6층</t>
+        </is>
+      </c>
+      <c r="K25" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L25" s="87" t="inlineStr">
+        <is>
+          <t>설계2실</t>
+        </is>
+      </c>
+      <c r="M25" s="87" t="inlineStr">
+        <is>
+          <t>오한솔</t>
+        </is>
+      </c>
+      <c r="N25" s="87" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="I26" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K26" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L26" s="87" t="inlineStr">
+        <is>
+          <t>신사업개발실</t>
+        </is>
+      </c>
+      <c r="M26" s="87" t="inlineStr">
+        <is>
+          <t>최진달미</t>
+        </is>
+      </c>
+      <c r="N26" s="87" t="inlineStr">
+        <is>
+          <t>전무</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="I27" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K27" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L27" s="87" t="inlineStr">
+        <is>
+          <t>신사업개발실</t>
+        </is>
+      </c>
+      <c r="M27" s="87" t="inlineStr">
+        <is>
+          <t>박종철</t>
+        </is>
+      </c>
+      <c r="N27" s="87" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="I28" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K28" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L28" s="87" t="inlineStr">
+        <is>
+          <t>신사업개발실</t>
+        </is>
+      </c>
+      <c r="M28" s="87" t="inlineStr">
+        <is>
+          <t>이정진</t>
+        </is>
+      </c>
+      <c r="N28" s="87" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="I29" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K29" s="87" t="inlineStr">
+        <is>
+          <t>설계본부</t>
+        </is>
+      </c>
+      <c r="L29" s="87" t="inlineStr">
+        <is>
+          <t>신사업개발실</t>
+        </is>
+      </c>
+      <c r="M29" s="87" t="inlineStr">
+        <is>
+          <t>김순성</t>
+        </is>
+      </c>
+      <c r="N29" s="87" t="inlineStr">
+        <is>
+          <t>고문</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="I30" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K30" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L30" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="M30" s="87" t="inlineStr">
+        <is>
+          <t>김동우</t>
+        </is>
+      </c>
+      <c r="N30" s="87" t="inlineStr">
+        <is>
+          <t>전무</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="I31" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K31" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L31" s="87" t="inlineStr">
+        <is>
+          <t>사업관리실</t>
+        </is>
+      </c>
+      <c r="M31" s="87" t="inlineStr">
+        <is>
+          <t>이성규</t>
+        </is>
+      </c>
+      <c r="N31" s="87" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="I32" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K32" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L32" s="87" t="inlineStr">
+        <is>
+          <t>사업관리실</t>
+        </is>
+      </c>
+      <c r="M32" s="87" t="inlineStr">
+        <is>
+          <t>이강호</t>
+        </is>
+      </c>
+      <c r="N32" s="87" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="I33" s="87" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K33" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L33" s="87" t="inlineStr">
+        <is>
+          <t>사업관리실</t>
+        </is>
+      </c>
+      <c r="M33" s="87" t="inlineStr">
+        <is>
+          <t>김동규</t>
+        </is>
+      </c>
+      <c r="N33" s="87" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="I34" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K34" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L34" s="87" t="inlineStr">
+        <is>
+          <t>사업관리실</t>
+        </is>
+      </c>
+      <c r="M34" s="87" t="inlineStr">
+        <is>
+          <t>이완구</t>
+        </is>
+      </c>
+      <c r="N34" s="87" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="I35" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K35" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L35" s="87" t="inlineStr">
+        <is>
+          <t>영업관리실</t>
+        </is>
+      </c>
+      <c r="M35" s="87" t="inlineStr">
+        <is>
+          <t>주현철</t>
+        </is>
+      </c>
+      <c r="N35" s="87" t="inlineStr">
+        <is>
+          <t>상무</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="I36" s="87" t="n">
+        <v>11</v>
+      </c>
+      <c r="J36" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K36" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L36" s="87" t="inlineStr">
+        <is>
+          <t>영업관리실</t>
+        </is>
+      </c>
+      <c r="M36" s="87" t="inlineStr">
+        <is>
+          <t>문광정</t>
+        </is>
+      </c>
+      <c r="N36" s="87" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="I37" s="87" t="n">
+        <v>12</v>
+      </c>
+      <c r="J37" s="87" t="inlineStr">
+        <is>
+          <t>13층</t>
+        </is>
+      </c>
+      <c r="K37" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L37" s="87" t="inlineStr">
+        <is>
+          <t>영업관리실</t>
+        </is>
+      </c>
+      <c r="M37" s="87" t="inlineStr">
+        <is>
+          <t>이현섭</t>
+        </is>
+      </c>
+      <c r="N37" s="87" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="I38" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="J38" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K38" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L38" s="87" t="inlineStr">
+        <is>
+          <t>영업관리실</t>
+        </is>
+      </c>
+      <c r="M38" s="87" t="inlineStr">
+        <is>
+          <t>김진규</t>
+        </is>
+      </c>
+      <c r="N38" s="87" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="I39" s="87" t="n">
+        <v>14</v>
+      </c>
+      <c r="J39" s="87" t="inlineStr">
+        <is>
+          <t>11층</t>
+        </is>
+      </c>
+      <c r="K39" s="87" t="inlineStr">
+        <is>
+          <t>사업관리본부</t>
+        </is>
+      </c>
+      <c r="L39" s="87" t="inlineStr">
+        <is>
+          <t>영업관리실</t>
+        </is>
+      </c>
+      <c r="M39" s="87" t="inlineStr">
+        <is>
+          <t>연지현</t>
+        </is>
+      </c>
+      <c r="N39" s="87" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5906,7 +7586,7 @@
       <c r="E1" s="42" t="n">
         <v>385770</v>
       </c>
-      <c r="F1" s="92" t="inlineStr">
+      <c r="F1" s="95" t="inlineStr">
         <is>
           <t>미납전기료(예다여성의원)</t>
         </is>
@@ -6183,12 +7863,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="93" t="n"/>
-      <c r="B7" s="94" t="n"/>
-      <c r="C7" s="95" t="n"/>
-      <c r="D7" s="96" t="n"/>
-      <c r="E7" s="96" t="n"/>
-      <c r="F7" s="97" t="n"/>
+      <c r="A7" s="96" t="n"/>
+      <c r="B7" s="97" t="n"/>
+      <c r="C7" s="98" t="n"/>
+      <c r="D7" s="99" t="n"/>
+      <c r="E7" s="99" t="n"/>
+      <c r="F7" s="100" t="n"/>
       <c r="I7" s="22" t="n">
         <v>6</v>
       </c>
@@ -7795,7 +9475,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7997,7 +9677,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C5" s="98">
+      <c r="C5" s="101">
         <f>COUNTIF(L:L,"영업관리실")-1</f>
         <v/>
       </c>
@@ -8049,7 +9729,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C6" s="98">
+      <c r="C6" s="101">
         <f>COUNTIF(L:L,"사업관리실")</f>
         <v/>
       </c>
@@ -8205,7 +9885,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C9" s="98">
+      <c r="C9" s="101">
         <f>COUNTIF(L:L,"사업관리본부")</f>
         <v/>
       </c>
@@ -8257,7 +9937,7 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="C10" s="98">
+      <c r="C10" s="101">
         <f>COUNTIF(L:L,"설계본부")</f>
         <v/>
       </c>
@@ -8309,7 +9989,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C11" s="98">
+      <c r="C11" s="101">
         <f>COUNTIF(L:L,"전사")</f>
         <v/>
       </c>
@@ -8606,7 +10286,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C18" s="98">
+      <c r="C18" s="101">
         <f>COUNTIF(L:L,"감사역")</f>
         <v/>
       </c>
@@ -8662,7 +10342,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C19" s="98" t="n">
+      <c r="C19" s="101" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="73">
@@ -8717,7 +10397,7 @@
           <t>연구</t>
         </is>
       </c>
-      <c r="C20" s="98">
+      <c r="C20" s="101">
         <f>COUNTIF(L:L,"R&amp;D본부")</f>
         <v/>
       </c>
@@ -9362,7 +11042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9443,7 +11123,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C5" s="98" t="n">
+      <c r="C5" s="101" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="73">
@@ -9470,7 +11150,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C6" s="98" t="n">
+      <c r="C6" s="101" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="73">
@@ -9551,7 +11231,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C9" s="98" t="n">
+      <c r="C9" s="101" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="73">
@@ -9578,7 +11258,7 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="C10" s="98" t="n">
+      <c r="C10" s="101" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="73" t="n">
@@ -9603,7 +11283,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C11" s="98" t="n">
+      <c r="C11" s="101" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="73">
@@ -9713,7 +11393,7 @@
           <t>판관</t>
         </is>
       </c>
-      <c r="C18" s="98" t="n">
+      <c r="C18" s="101" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="73">
@@ -9740,7 +11420,7 @@
           <t>연구</t>
         </is>
       </c>
-      <c r="C19" s="98" t="n">
+      <c r="C19" s="101" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="73">
